--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97529</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107002</v>
+        <v>107003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92027</v>
+        <v>92028</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107003</v>
+        <v>107005</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92028</v>
+        <v>92029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107005</v>
+        <v>107006</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92029</v>
+        <v>92030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107006</v>
+        <v>107007</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107007</v>
+        <v>107013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 57028-2021 artfynd.xlsx
+++ b/artfynd/A 57028-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136048568</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136048569</v>
       </c>
       <c r="B3" t="n">
-        <v>92036</v>
+        <v>92037</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>136048565</v>
       </c>
       <c r="B5" t="n">
-        <v>107013</v>
+        <v>107014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
